--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:38</t>
+    <t xml:space="preserve">2026-09-09 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:24</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -42,87 +42,87 @@
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
+    <t xml:space="preserve">Futaleufú</t>
+  </si>
+  <si>
     <t xml:space="preserve">Puyehue</t>
   </si>
   <si>
-    <t xml:space="preserve">Futaleufú</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puerto Octay</t>
   </si>
   <si>
     <t xml:space="preserve">Puerto Varas</t>
   </si>
   <si>
+    <t xml:space="preserve">Chaitén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hualaihué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Negro</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Juan de la Costa</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaitén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Negro</t>
+    <t xml:space="preserve">Frutillar</t>
   </si>
   <si>
     <t xml:space="preserve">Cochamó</t>
   </si>
   <si>
-    <t xml:space="preserve">Frutillar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hualaihué</t>
-  </si>
-  <si>
     <t xml:space="preserve">Llanquihue</t>
   </si>
   <si>
+    <t xml:space="preserve">Fresia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Maullín</t>
   </si>
   <si>
-    <t xml:space="preserve">Fresia</t>
+    <t xml:space="preserve">Curaco de Vélez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalcahue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chonchi</t>
   </si>
   <si>
     <t xml:space="preserve">Purranque</t>
   </si>
   <si>
+    <t xml:space="preserve">Queilén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Los Muermos</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalcahue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chonchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curaco de Vélez</t>
+    <t xml:space="preserve">Puqueldón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quemchi</t>
   </si>
   <si>
     <t xml:space="preserve">Castro</t>
   </si>
   <si>
-    <t xml:space="preserve">Queilén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puqueldón</t>
-  </si>
-  <si>
     <t xml:space="preserve">Puerto Montt</t>
   </si>
   <si>
+    <t xml:space="preserve">Quinchao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quellón</t>
+  </si>
+  <si>
     <t xml:space="preserve">Osorno</t>
   </si>
   <si>
-    <t xml:space="preserve">Quemchi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinchao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quellón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancud</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calbuco</t>
   </si>
   <si>
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>58.42</v>
+        <v>27.71</v>
       </c>
     </row>
     <row r="3">
@@ -588,7 +588,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>58.07</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="4">
@@ -599,13 +599,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10304</v>
+        <v>10402</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>53.06</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="5">
@@ -616,13 +616,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10402</v>
+        <v>10304</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>51.23</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="6">
@@ -639,7 +639,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>49.02</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>46.5</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="8">
@@ -667,13 +667,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10306</v>
+        <v>10401</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>46.48</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="9">
@@ -684,13 +684,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10401</v>
+        <v>10403</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>46.17</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="10">
@@ -707,7 +707,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>44.39</v>
+        <v>19.56</v>
       </c>
     </row>
     <row r="11">
@@ -718,13 +718,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>10103</v>
+        <v>10306</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>39.4</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>38.25</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="13">
@@ -752,13 +752,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>10403</v>
+        <v>10103</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37.67</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="14">
@@ -775,7 +775,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>36.42</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="15">
@@ -786,13 +786,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>10108</v>
+        <v>10104</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>33.24</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="16">
@@ -803,13 +803,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>10104</v>
+        <v>10108</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>33.02</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="17">
@@ -820,13 +820,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>10303</v>
+        <v>10204</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>32.75</v>
+        <v>14.17</v>
       </c>
     </row>
     <row r="18">
@@ -837,13 +837,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>10106</v>
+        <v>10205</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>32.1</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="19">
@@ -854,13 +854,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>10205</v>
+        <v>10203</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>31.74</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="20">
@@ -871,13 +871,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>10203</v>
+        <v>10303</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>30.34</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="21">
@@ -888,13 +888,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10204</v>
+        <v>10207</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>28.86</v>
+        <v>13.6</v>
       </c>
     </row>
     <row r="22">
@@ -905,13 +905,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>10201</v>
+        <v>10106</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>28.61</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="23">
@@ -922,13 +922,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>10207</v>
+        <v>10206</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>27.28</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="24">
@@ -939,13 +939,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>10206</v>
+        <v>10209</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>26.9</v>
+        <v>12.33</v>
       </c>
     </row>
     <row r="25">
@@ -956,13 +956,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>10101</v>
+        <v>10201</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>26.68</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="26">
@@ -973,13 +973,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>10301</v>
+        <v>10101</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>26.65</v>
+        <v>11.98</v>
       </c>
     </row>
     <row r="27">
@@ -990,13 +990,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>10209</v>
+        <v>10210</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>26.54</v>
+        <v>11.94</v>
       </c>
     </row>
     <row r="28">
@@ -1007,13 +1007,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>10210</v>
+        <v>10202</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>26.27</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="29">
@@ -1030,7 +1030,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>25.55</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="30">
@@ -1041,13 +1041,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>10202</v>
+        <v>10301</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>24.84</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>23.67</v>
+        <v>11.08</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:18</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -571,7 +571,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27.71</v>
+        <v>277.08</v>
       </c>
     </row>
     <row r="3">
@@ -588,7 +588,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>25.59</v>
+        <v>255.94</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>25.44</v>
+        <v>254.39</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24.92</v>
+        <v>249.21</v>
       </c>
     </row>
     <row r="6">
@@ -639,7 +639,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>22.82</v>
+        <v>228.2</v>
       </c>
     </row>
     <row r="7">
@@ -656,7 +656,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.11</v>
+        <v>211.08</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +673,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.78</v>
+        <v>197.79</v>
       </c>
     </row>
     <row r="9">
@@ -690,7 +690,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>19.58</v>
+        <v>195.77</v>
       </c>
     </row>
     <row r="10">
@@ -707,7 +707,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>19.56</v>
+        <v>195.63</v>
       </c>
     </row>
     <row r="11">
@@ -724,7 +724,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>19.33</v>
+        <v>193.26</v>
       </c>
     </row>
     <row r="12">
@@ -741,7 +741,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>18.08</v>
+        <v>180.81</v>
       </c>
     </row>
     <row r="13">
@@ -758,7 +758,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>17.9</v>
+        <v>178.99</v>
       </c>
     </row>
     <row r="14">
@@ -775,7 +775,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>17.05</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="15">
@@ -792,7 +792,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.99</v>
+        <v>149.93</v>
       </c>
     </row>
     <row r="16">
@@ -809,7 +809,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14.77</v>
+        <v>147.71</v>
       </c>
     </row>
     <row r="17">
@@ -826,7 +826,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>14.17</v>
+        <v>141.66</v>
       </c>
     </row>
     <row r="18">
@@ -843,7 +843,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14.12</v>
+        <v>141.19</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +860,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>13.91</v>
+        <v>139.06</v>
       </c>
     </row>
     <row r="20">
@@ -877,7 +877,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>13.82</v>
+        <v>138.17</v>
       </c>
     </row>
     <row r="21">
@@ -894,7 +894,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>13.6</v>
+        <v>135.95</v>
       </c>
     </row>
     <row r="22">
@@ -911,7 +911,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>13.46</v>
+        <v>134.6</v>
       </c>
     </row>
     <row r="23">
@@ -928,7 +928,7 @@
         <v>2022</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>12.66</v>
+        <v>126.58</v>
       </c>
     </row>
     <row r="24">
@@ -945,7 +945,7 @@
         <v>2022</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12.33</v>
+        <v>123.34</v>
       </c>
     </row>
     <row r="25">
@@ -962,7 +962,7 @@
         <v>2022</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>12.18</v>
+        <v>121.81</v>
       </c>
     </row>
     <row r="26">
@@ -979,7 +979,7 @@
         <v>2022</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11.98</v>
+        <v>119.77</v>
       </c>
     </row>
     <row r="27">
@@ -996,7 +996,7 @@
         <v>2022</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>11.94</v>
+        <v>119.39</v>
       </c>
     </row>
     <row r="28">
@@ -1013,7 +1013,7 @@
         <v>2022</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>11.93</v>
+        <v>119.29</v>
       </c>
     </row>
     <row r="29">
@@ -1030,7 +1030,7 @@
         <v>2022</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>11.7</v>
+        <v>116.98</v>
       </c>
     </row>
     <row r="30">
@@ -1047,7 +1047,7 @@
         <v>2022</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>11.59</v>
+        <v>115.93</v>
       </c>
     </row>
     <row r="31">
@@ -1064,7 +1064,7 @@
         <v>2022</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>11.08</v>
+        <v>110.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:08</t>
+    <t xml:space="preserve">2026-10-05 07:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
